--- a/src/main/resources/reports/apk_8.xlsx
+++ b/src/main/resources/reports/apk_8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="8.1" sheetId="1" state="visible" r:id="rId2"/>
@@ -92,10 +92,10 @@
 (с 1 января по 31 декабря)</t>
   </si>
   <si>
-    <t xml:space="preserve">2023 год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 год</t>
+    <t xml:space="preserve">2026 год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 год</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/src/main/resources/reports/apk_8.xlsx
+++ b/src/main/resources/reports/apk_8.xlsx
@@ -915,7 +915,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -926,18 +926,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E0B4"/>
-        <bgColor rgb="FFAFD095"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FFC5E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1024,7 +1012,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1053,7 +1041,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1065,7 +1053,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1073,11 +1061,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1085,11 +1073,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1097,10 +1085,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="6" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1109,10 +1093,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1121,19 +1101,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1146,66 +1118,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC5E0B4"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1343,11 +1255,11 @@
       <c r="B10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -1364,7 +1276,7 @@
       <c r="A12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="10"/>
@@ -1437,8 +1349,8 @@
       <c r="B18" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
@@ -1595,8 +1507,8 @@
       <c r="B29" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
@@ -1619,18 +1531,18 @@
       <c r="B31" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1669,12 +1581,12 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -1761,10 +1673,10 @@
       <c r="B9" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="10" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1775,10 +1687,10 @@
       <c r="B10" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="22" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1789,10 +1701,10 @@
       <c r="B11" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="22" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1804,7 +1716,7 @@
         <v>109</v>
       </c>
       <c r="C12" s="10"/>
-      <c r="D12" s="24"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
@@ -1813,10 +1725,10 @@
       <c r="B13" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="22" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1827,10 +1739,10 @@
       <c r="B14" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="22" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1857,10 +1769,10 @@
       <c r="B16" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="23" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1871,10 +1783,10 @@
       <c r="B17" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="23" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1885,10 +1797,10 @@
       <c r="B18" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="23" t="s">
         <v>131</v>
       </c>
     </row>
